--- a/DGT Junio 26.xlsx
+++ b/DGT Junio 26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jorge/Desktop/AUTOESCUELA/datos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C28B64DA-A04B-4846-9D47-BDD9E6670991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D65F64E4-A13C-144F-B6B3-A74AE93B3016}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="720" windowWidth="23220" windowHeight="16820" xr2:uid="{AE6512D7-AD52-4543-8CDE-87DCF5042393}"/>
   </bookViews>
@@ -446,7 +446,7 @@
     <t>De las siguientes ADAS ¿Cuál es conocido con el nombre de Alerta de trafico cruzado?</t>
   </si>
   <si>
-    <t>imágenes/resalto.png</t>
+    <t>imagenes/resalto.png</t>
   </si>
 </sst>
 </file>
